--- a/data/trans_dic/P16A06-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A06-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,06</t>
+          <t>1,77; 3,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,67</t>
+          <t>4,24; 7,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 14,27</t>
+          <t>9,28; 14,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,67</t>
+          <t>5,64; 8,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,62; 12,08</t>
+          <t>8,63; 11,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,93; 17,5</t>
+          <t>12,87; 17,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,04; 25,28</t>
+          <t>19,93; 24,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 6,47</t>
+          <t>4,68; 6,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 8,07</t>
+          <t>5,93; 8,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,66; 12,68</t>
+          <t>9,65; 12,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 19,96</t>
+          <t>16,52; 20,07</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,86</t>
+          <t>0,76; 1,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,5</t>
+          <t>1,24; 2,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,3</t>
+          <t>1,14; 2,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,6</t>
+          <t>2,5; 4,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,27</t>
+          <t>1,79; 3,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,41</t>
+          <t>3,37; 5,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,95</t>
+          <t>3,92; 6,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 8,15</t>
+          <t>5,14; 8,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,35</t>
+          <t>1,41; 2,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,55</t>
+          <t>2,44; 3,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 3,79</t>
+          <t>2,63; 3,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 6,08</t>
+          <t>4,12; 5,99</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,24</t>
+          <t>0,34; 2,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,86</t>
+          <t>0,67; 3,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,61</t>
+          <t>0,86; 3,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,82</t>
+          <t>2,73; 5,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,54</t>
+          <t>0,86; 3,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,04</t>
+          <t>1,3; 5,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,21</t>
+          <t>2,18; 5,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,21</t>
+          <t>4,32; 7,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,23</t>
+          <t>0,76; 2,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,04</t>
+          <t>1,29; 3,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,86</t>
+          <t>1,85; 3,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,97</t>
+          <t>3,91; 6,03</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,47</t>
+          <t>1,53; 2,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,63</t>
+          <t>1,51; 2,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,2</t>
+          <t>2,1; 3,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,67</t>
+          <t>3,77; 5,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,86</t>
+          <t>3,5; 4,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 7,14</t>
+          <t>5,39; 7,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 8,52</t>
+          <t>6,7; 8,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 10,96</t>
+          <t>8,01; 10,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,54</t>
+          <t>2,65; 3,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 4,7</t>
+          <t>3,71; 4,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 5,66</t>
+          <t>4,59; 5,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 8,15</t>
+          <t>6,48; 8,14</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28122; 52745</t>
+          <t>28195; 52752</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17674; 39391</t>
+          <t>17160; 38021</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31606; 57888</t>
+          <t>31976; 59538</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48566; 73279</t>
+          <t>47674; 72181</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>76669; 113985</t>
+          <t>74228; 111939</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>114905; 160952</t>
+          <t>114945; 158928</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>128631; 174095</t>
+          <t>127975; 174563</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>150606; 190030</t>
+          <t>149768; 187418</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>109072; 151784</t>
+          <t>109743; 155001</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134457; 185868</t>
+          <t>136621; 191040</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>169036; 221797</t>
+          <t>168782; 221114</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>208011; 252532</t>
+          <t>209033; 253931</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12351; 31458</t>
+          <t>12820; 31765</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23447; 49034</t>
+          <t>24224; 50677</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23813; 47835</t>
+          <t>23630; 49998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56972; 105267</t>
+          <t>57230; 104562</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27057; 51848</t>
+          <t>28481; 53136</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59305; 94799</t>
+          <t>58956; 96636</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76954; 118269</t>
+          <t>77882; 119611</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>109572; 182374</t>
+          <t>115077; 182712</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44274; 77003</t>
+          <t>46345; 77891</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>88769; 131653</t>
+          <t>90431; 130854</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>109612; 154018</t>
+          <t>107077; 154900</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>192705; 275233</t>
+          <t>186350; 271032</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1970; 12361</t>
+          <t>1890; 11354</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3207; 18563</t>
+          <t>3213; 19079</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4863; 19715</t>
+          <t>4706; 19412</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17454; 37653</t>
+          <t>17669; 38303</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3909; 16862</t>
+          <t>4078; 16681</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6402; 23043</t>
+          <t>5948; 23072</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10548; 28595</t>
+          <t>11993; 31089</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28362; 47618</t>
+          <t>28518; 47925</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7845; 22921</t>
+          <t>7788; 23819</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12827; 37874</t>
+          <t>12079; 35184</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19359; 42329</t>
+          <t>20304; 43175</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50339; 78036</t>
+          <t>51162; 78866</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50520; 80965</t>
+          <t>50187; 82874</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52435; 89564</t>
+          <t>51552; 88543</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71975; 108105</t>
+          <t>71012; 107619</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126313; 195545</t>
+          <t>130108; 196592</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>116772; 164191</t>
+          <t>118361; 165057</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>193116; 252950</t>
+          <t>190936; 253363</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>236084; 301009</t>
+          <t>236514; 299490</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>301155; 399897</t>
+          <t>292216; 399838</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180172; 235616</t>
+          <t>176275; 233535</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>254893; 326812</t>
+          <t>257603; 326539</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>317135; 391131</t>
+          <t>316844; 394373</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>459204; 578687</t>
+          <t>460161; 578054</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A06-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A06-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,11</t>
+          <t>2,81; 5,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,92</t>
+          <t>1,72; 3,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,89</t>
+          <t>4,43; 7,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,28; 14,06</t>
+          <t>8,74; 13,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 8,51</t>
+          <t>5,74; 8,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,93</t>
+          <t>8,56; 11,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,87; 17,55</t>
+          <t>12,81; 17,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,93; 24,94</t>
+          <t>19,67; 23,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,6</t>
+          <t>4,66; 6,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,29</t>
+          <t>5,89; 8,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,65; 12,64</t>
+          <t>9,58; 12,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,52; 20,07</t>
+          <t>15,7; 18,89</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,88</t>
+          <t>0,73; 1,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,59</t>
+          <t>1,15; 2,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,41</t>
+          <t>1,17; 2,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,57</t>
+          <t>3,3; 5,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,35</t>
+          <t>1,76; 3,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,52</t>
+          <t>3,35; 5,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,02</t>
+          <t>3,92; 5,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,17</t>
+          <t>6,75; 8,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,37</t>
+          <t>1,37; 2,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,53</t>
+          <t>2,39; 3,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,81</t>
+          <t>2,68; 3,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 5,99</t>
+          <t>5,29; 6,58</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,06</t>
+          <t>0,37; 2,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,97</t>
+          <t>0,65; 4,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,55</t>
+          <t>0,88; 3,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,92</t>
+          <t>2,53; 5,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,5</t>
+          <t>0,85; 3,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,04</t>
+          <t>1,3; 4,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,66</t>
+          <t>1,97; 5,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,26</t>
+          <t>4,33; 7,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,32</t>
+          <t>0,78; 2,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,75</t>
+          <t>1,31; 3,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,94</t>
+          <t>1,78; 3,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,03</t>
+          <t>3,87; 5,91</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,53</t>
+          <t>1,57; 2,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,6</t>
+          <t>1,52; 2,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,19</t>
+          <t>2,08; 3,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,7</t>
+          <t>4,44; 5,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,88</t>
+          <t>3,51; 4,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,39; 7,15</t>
+          <t>5,46; 7,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 8,48</t>
+          <t>6,59; 8,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,01; 10,96</t>
+          <t>9,59; 11,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 3,51</t>
+          <t>2,71; 3,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,7</t>
+          <t>3,68; 4,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 5,71</t>
+          <t>4,65; 5,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,14</t>
+          <t>7,35; 8,46</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60131</t>
+          <t>63293</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>168449</t>
+          <t>177500</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>228579</t>
+          <t>240793</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28195; 52752</t>
+          <t>28996; 52347</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17160; 38021</t>
+          <t>16710; 38165</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31976; 59538</t>
+          <t>33429; 59657</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47674; 72181</t>
+          <t>50415; 77046</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74228; 111939</t>
+          <t>75462; 114004</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>114945; 158928</t>
+          <t>114093; 159234</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>127975; 174563</t>
+          <t>127427; 175232</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>149768; 187418</t>
+          <t>161085; 196238</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>109743; 155001</t>
+          <t>109250; 153664</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136621; 191040</t>
+          <t>135604; 186634</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168782; 221114</t>
+          <t>167591; 223673</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>209033; 253931</t>
+          <t>219179; 263688</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81622</t>
+          <t>90828</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>153600</t>
+          <t>167539</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>235222</t>
+          <t>258368</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12820; 31765</t>
+          <t>12425; 31307</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24224; 50677</t>
+          <t>22561; 46649</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23630; 49998</t>
+          <t>24200; 47806</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57230; 104562</t>
+          <t>73510; 112124</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28481; 53136</t>
+          <t>28008; 55311</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58956; 96636</t>
+          <t>58705; 94248</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77882; 119611</t>
+          <t>78013; 117676</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>115077; 182712</t>
+          <t>146505; 187648</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46345; 77891</t>
+          <t>44965; 78227</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90431; 130854</t>
+          <t>88660; 130704</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107077; 154900</t>
+          <t>109124; 160458</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>186350; 271032</t>
+          <t>232610; 289687</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>27651</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37280</t>
+          <t>41521</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63310</t>
+          <t>69171</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1890; 11354</t>
+          <t>2045; 11502</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3213; 19079</t>
+          <t>3133; 19570</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4706; 19412</t>
+          <t>4816; 19895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17669; 38303</t>
+          <t>18010; 39136</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4078; 16681</t>
+          <t>4027; 17865</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5948; 23072</t>
+          <t>5932; 22522</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11993; 31089</t>
+          <t>10808; 29217</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28518; 47925</t>
+          <t>31765; 52915</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7788; 23819</t>
+          <t>8035; 23186</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12079; 35184</t>
+          <t>12267; 34010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20304; 43175</t>
+          <t>19561; 42472</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51162; 78866</t>
+          <t>55988; 85484</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167783</t>
+          <t>181771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>359329</t>
+          <t>386561</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>527112</t>
+          <t>568332</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50187; 82874</t>
+          <t>51342; 83533</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51552; 88543</t>
+          <t>51928; 87894</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71012; 107619</t>
+          <t>70171; 108003</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130108; 196592</t>
+          <t>156142; 208119</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>118361; 165057</t>
+          <t>118772; 165490</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>190936; 253363</t>
+          <t>193360; 253467</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>236514; 299490</t>
+          <t>232863; 301597</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>292216; 399838</t>
+          <t>357138; 416134</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>176275; 233535</t>
+          <t>180315; 234048</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>257603; 326539</t>
+          <t>255695; 326028</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>316844; 394373</t>
+          <t>321088; 394299</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>460161; 578054</t>
+          <t>532566; 612508</t>
         </is>
       </c>
     </row>
